--- a/scripts/recalc/texts.xlsx
+++ b/scripts/recalc/texts.xlsx
@@ -7619,9 +7619,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="0" t="e">
+      <c r="A142" s="0">
         <f>LEN(_xlfn.TEXTJOIN(",",FALSE,Data!B:B))</f>
-        <v>#VALUE!</v>
       </c>
     </row>
     <row r="143">
